--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486506_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486506_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5385</v>
+        <v>4.6938</v>
       </c>
       <c r="E2" t="n">
-        <v>3.229</v>
+        <v>3.3228</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3094</v>
+        <v>1.3711</v>
       </c>
       <c r="G2" t="n">
         <v>1.1315</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.853</v>
+        <v>-0.6976</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5564</v>
+        <v>-0.4626</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2966</v>
+        <v>-0.2349</v>
       </c>
       <c r="V2" t="n">
         <v>3.3899</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5451</v>
+        <v>2.8053</v>
       </c>
       <c r="E3" t="n">
-        <v>0.93</v>
+        <v>1.067</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6151</v>
+        <v>1.7384</v>
       </c>
       <c r="G3" t="n">
         <v>0.4389</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9368</v>
+        <v>-0.6766</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6813</v>
+        <v>-0.5444</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2555</v>
+        <v>-0.1322</v>
       </c>
       <c r="V3" t="n">
         <v>1.5204</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.011</v>
+        <v>-0.8933</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.8784</v>
+        <v>-1.8532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.9598</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2097</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4539</v>
+        <v>-0.3362</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2139</v>
+        <v>-0.1887</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.24</v>
+        <v>-0.1475</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2169</v>
+        <v>-1.1232</v>
       </c>
       <c r="E5" t="n">
-        <v>3.138</v>
+        <v>3.2317</v>
       </c>
       <c r="F5" t="n">
         <v>-4.3549</v>
@@ -844,10 +844,10 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3425</v>
+        <v>-0.2488</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2704</v>
+        <v>-0.1766</v>
       </c>
       <c r="U5" t="n">
         <v>-0.0721</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8784</v>
+        <v>-1.5007</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3673</v>
+        <v>-1.1839</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.2457</v>
+        <v>-0.3168</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4867</v>
+        <v>2.7262</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9855</v>
+        <v>0.2982</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5012</v>
+        <v>2.428</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5741000000000001</v>
+        <v>2.7416</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4594</v>
+        <v>0.6363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1147</v>
+        <v>2.1053</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0608</v>
+        <v>-0.0154</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4449</v>
+        <v>-0.3381</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.616</v>
+        <v>0.3227</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>-4.3501</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9335</v>
+        <v>-0.9866</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0106</v>
+        <v>-0.7054</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0772</v>
+        <v>-0.2812</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>-1.3252</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0487</v>
+        <v>-1.638</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8581</v>
+        <v>-0.3859</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1905</v>
+        <v>-1.2522</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9168</v>
@@ -1000,13 +1000,13 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5446</v>
+        <v>-0.134</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6165</v>
+        <v>-0.1442</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="V7" t="n">
         <v>0.1952</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1182</v>
+        <v>-1.8733</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5735</v>
+        <v>-2.9895</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4553</v>
+        <v>1.1162</v>
       </c>
       <c r="G8" t="n">
         <v>0.1381</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1237</v>
+        <v>-0.8787</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4384</v>
+        <v>-0.8544</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3147</v>
+        <v>-0.0244</v>
       </c>
       <c r="V8" t="n">
         <v>1.695</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.208</v>
+        <v>-2.6971</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7679</v>
+        <v>0.6102</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4401</v>
+        <v>-3.3073</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7262</v>
+        <v>-1.4867</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2982</v>
+        <v>-0.9855</v>
       </c>
       <c r="I9" t="n">
-        <v>2.428</v>
+        <v>-0.5012</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7416</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6363</v>
+        <v>0.4594</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1053</v>
+        <v>0.1147</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0154</v>
+        <v>-2.0608</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3381</v>
+        <v>-1.4449</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3227</v>
+        <v>-0.616</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.0451</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.3501</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6939</v>
+        <v>0.1148</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2894</v>
+        <v>0.2536</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4045</v>
+        <v>-0.1388</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.3252</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0293</v>
+        <v>-3.2344</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9435</v>
+        <v>-2.2102</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0858</v>
+        <v>-1.0242</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5414</v>
@@ -1234,13 +1234,13 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2947</v>
+        <v>0.0895</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4831</v>
+        <v>0.2163</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1884</v>
+        <v>-0.1268</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7855</v>
+        <v>-3.3817</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9419</v>
+        <v>-1.5381</v>
       </c>
       <c r="F11" t="n">
         <v>-1.8436</v>
@@ -1312,10 +1312,10 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7775</v>
+        <v>-0.3737</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.3377</v>
       </c>
       <c r="U11" t="n">
         <v>-0.0361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.2124</v>
+        <v>-8.842599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.299</v>
+        <v>-1.9291</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.913399999999999</v>
+        <v>-6.913500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-8.231999999999999</v>
@@ -1360,7 +1360,7 @@
         <v>-2.4946</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.7374</v>
+        <v>-5.737400000000001</v>
       </c>
       <c r="J12" t="n">
         <v>0.3321000000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-4.5464</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.2627</v>
+        <v>-3.262700000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.9627</v>
@@ -1390,10 +1390,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.497699999999999</v>
+        <v>-4.1279</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.314</v>
+        <v>-2.9441</v>
       </c>
       <c r="U12" t="n">
         <v>-1.1838</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,37 +1423,37 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8224</v>
+        <v>4.0656</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1832</v>
+        <v>3.6673</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3608</v>
+        <v>0.3983</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7927</v>
+        <v>1.3238</v>
       </c>
       <c r="H13" t="n">
-        <v>2.105</v>
+        <v>0.891</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3124</v>
+        <v>0.4327</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9794</v>
+        <v>2.693</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8048</v>
+        <v>1.7734</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1745</v>
+        <v>0.9196</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1867</v>
+        <v>-1.3692</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6998</v>
+        <v>-0.8823</v>
       </c>
       <c r="O13" t="n">
         <v>-0.4869</v>
@@ -1468,28 +1468,28 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0945</v>
+        <v>0.6766</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5312</v>
+        <v>-0.1334</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5633</v>
+        <v>0.8099</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3698</v>
+        <v>0.7602</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8902</v>
+        <v>1.3252</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2599</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5791</v>
+        <v>3.8455</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7106</v>
+        <v>4.9597</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8685</v>
+        <v>-1.1142</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2627</v>
+        <v>1.7927</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6308</v>
+        <v>2.105</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6319</v>
+        <v>-0.3124</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7744</v>
+        <v>2.9794</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4851</v>
+        <v>2.8048</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2893</v>
+        <v>0.1745</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4883</v>
+        <v>-1.1867</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1457</v>
+        <v>-0.6998</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3426</v>
+        <v>-0.4869</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07870000000000001</v>
+        <v>1.1176</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2139</v>
+        <v>0.3076</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2926</v>
+        <v>0.8099</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3252</v>
+        <v>-0.3698</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3252</v>
+        <v>1.8902</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9249</v>
+        <v>3.6857</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7732</v>
+        <v>1.8224</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1517</v>
+        <v>1.8633</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3238</v>
+        <v>3.2627</v>
       </c>
       <c r="H15" t="n">
-        <v>0.891</v>
+        <v>2.6308</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4327</v>
+        <v>0.6319</v>
       </c>
       <c r="J15" t="n">
-        <v>2.693</v>
+        <v>2.7744</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7734</v>
+        <v>2.4851</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9196</v>
+        <v>0.2893</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3692</v>
+        <v>0.4883</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8823</v>
+        <v>0.1457</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4869</v>
+        <v>0.3426</v>
       </c>
       <c r="P15" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4641</v>
+        <v>0.1854</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0274</v>
+        <v>-0.1021</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5633</v>
+        <v>0.2875</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7602</v>
+        <v>1.3252</v>
       </c>
       <c r="W15" t="n">
         <v>1.3252</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.502</v>
+        <v>1.624</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5855</v>
+        <v>-0.3861</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0835</v>
+        <v>2.0101</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3556</v>
+        <v>1.5354</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0551</v>
+        <v>1.4931</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3005</v>
+        <v>0.0422</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1038</v>
+        <v>0.7976</v>
       </c>
       <c r="K16" t="n">
-        <v>0.146</v>
+        <v>0.949</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9578</v>
+        <v>-0.1514</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2518</v>
+        <v>0.7378</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9091</v>
+        <v>0.5442</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3426</v>
+        <v>0.1936</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.514</v>
+        <v>0.5236</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4817</v>
+        <v>0.1214</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0323</v>
+        <v>0.4023</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.0202</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3555</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7214</v>
+        <v>1.5797</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0768</v>
+        <v>-0.9654</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5354</v>
+        <v>2.3556</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4931</v>
+        <v>1.0551</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0422</v>
+        <v>1.3005</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7976</v>
+        <v>1.1038</v>
       </c>
       <c r="K17" t="n">
-        <v>0.949</v>
+        <v>0.146</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1514</v>
+        <v>0.9578</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7378</v>
+        <v>1.2518</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5442</v>
+        <v>0.9091</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1936</v>
+        <v>0.3426</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2551</v>
+        <v>0.6264</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2139</v>
+        <v>0.4759</v>
       </c>
       <c r="U17" t="n">
-        <v>0.469</v>
+        <v>0.1505</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-3.0202</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-3.0202</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0482</v>
+        <v>0.4081</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4669</v>
+        <v>0.1973</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4187</v>
+        <v>0.2108</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2081</v>
+        <v>-0.3784</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8726</v>
+        <v>-0.286</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6646</v>
+        <v>-0.0924</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1292</v>
+        <v>0.2225</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0238</v>
+        <v>0.146</v>
       </c>
       <c r="L18" t="n">
-        <v>0.153</v>
+        <v>0.0765</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3372</v>
+        <v>-0.6009</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8488</v>
+        <v>-0.432</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.1689</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1889</v>
+        <v>0.134</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2077</v>
+        <v>-0.0252</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9812</v>
+        <v>0.1592</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4552</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.5851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2521</v>
+        <v>0.1118</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5780999999999999</v>
+        <v>1.6846</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8302</v>
+        <v>-1.5728</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5668</v>
+        <v>-0.2081</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4325</v>
+        <v>-0.8726</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9993</v>
+        <v>0.6646</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8706</v>
+        <v>0.1292</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4681</v>
+        <v>-0.0238</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3387</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3038</v>
+        <v>-0.3372</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9643</v>
+        <v>-0.8488</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6606</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2726</v>
+        <v>1.2525</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5312</v>
+        <v>0.4254</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9347</v>
+        <v>-2.4552</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-3.5851</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1114</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.9134</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0259</v>
+        <v>0.8302</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3784</v>
+        <v>0.5668</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.286</v>
+        <v>-1.4325</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0924</v>
+        <v>1.9993</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2225</v>
+        <v>0.8706</v>
       </c>
       <c r="K20" t="n">
-        <v>0.146</v>
+        <v>-0.4681</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0765</v>
+        <v>1.3387</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6009</v>
+        <v>-0.3038</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.432</v>
+        <v>-0.9643</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1689</v>
+        <v>0.6606</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1627</v>
+        <v>0.9373</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.137</v>
+        <v>0.1959</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0257</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3151</v>
+        <v>-0.2913</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.695</v>
+        <v>-1.9127</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3798</v>
+        <v>1.6213</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8492</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1184</v>
+        <v>-0.0946</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8904</v>
+        <v>-0.1081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.228</v>
+        <v>0.0135</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3243</v>
+        <v>-1.2273</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.476</v>
+        <v>-2.7505</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8483000000000001</v>
+        <v>1.5233</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4667</v>
+        <v>-2.6359</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5026</v>
+        <v>-2.8798</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0359</v>
+        <v>0.2438</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1115</v>
+        <v>-2.5306</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9585</v>
+        <v>-2.6454</v>
       </c>
       <c r="L22" t="n">
-        <v>0.153</v>
+        <v>0.1147</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3553</v>
+        <v>-0.1053</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5442</v>
+        <v>-0.2344</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1889</v>
+        <v>0.1291</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8169</v>
+        <v>0.5387</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8051</v>
+        <v>-0.2199</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0118</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0854</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.0854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7437</v>
+        <v>-1.7957</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4211</v>
+        <v>-1.0348</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6774</v>
+        <v>-0.761</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6359</v>
+        <v>1.4667</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8798</v>
+        <v>1.5026</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2438</v>
+        <v>-0.0359</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5306</v>
+        <v>1.1115</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.6454</v>
+        <v>0.9585</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1147</v>
+        <v>0.153</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1053</v>
+        <v>0.3553</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2344</v>
+        <v>0.5442</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1291</v>
+        <v>-0.1889</v>
       </c>
       <c r="P23" t="n">
-        <v>0.87</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R23" t="n">
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0222</v>
+        <v>0.3455</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8904</v>
+        <v>0.2464</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9127</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.0854</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.2125</v>
+        <v>10.9577</v>
       </c>
       <c r="E24" t="n">
-        <v>6.913300000000002</v>
+        <v>6.913499999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>3.299</v>
+        <v>4.0439</v>
       </c>
       <c r="G24" t="n">
-        <v>8.232100000000001</v>
+        <v>8.232099999999999</v>
       </c>
       <c r="H24" t="n">
         <v>2.494399999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>5.737300000000001</v>
+        <v>5.737299999999999</v>
       </c>
       <c r="J24" t="n">
         <v>8.564399999999999</v>
@@ -2308,7 +2308,7 @@
         <v>4.546099999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3321000000000001</v>
+        <v>-0.3321000000000002</v>
       </c>
       <c r="N24" t="n">
         <v>-1.5233</v>
@@ -2317,22 +2317,22 @@
         <v>1.1911</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2625</v>
+        <v>3.262499999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8.700299999999999</v>
+        <v>-8.7003</v>
       </c>
       <c r="R24" t="n">
         <v>11.9625</v>
       </c>
       <c r="S24" t="n">
-        <v>5.497699999999998</v>
+        <v>6.243000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>1.1839</v>
       </c>
       <c r="U24" t="n">
-        <v>4.313899999999999</v>
+        <v>5.058999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-6.7799</v>
